--- a/backend/data/financials_by_company/1746.HK.xlsx
+++ b/backend/data/financials_by_company/1746.HK.xlsx
@@ -3660,7 +3660,7 @@
         <v>-2513000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>3.843</v>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
